--- a/docs/verification/files/rocscience/vp032a_fem.xlsx
+++ b/docs/verification/files/rocscience/vp032a_fem.xlsx
@@ -12361,10 +12361,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>40.0</v>
+        <v>-4.8</v>
       </c>
       <c r="C3" s="3">
-        <v>45.0</v>
+        <v>8.0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>22.639320225</v>
+        <v>-13.83</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -12388,20 +12388,10 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>42.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>48.0</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E4" s="3">
-        <v>20.0</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
